--- a/AAII_Financials/Quarterly/LDI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LDI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>LDI</t>
   </si>
@@ -656,127 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
@@ -786,89 +787,92 @@
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>308700</v>
+      </c>
+      <c r="E8" s="3">
         <v>295300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>321100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>335400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>281400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>290300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>188800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>363700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>248000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>185200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>192700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>258800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>264200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>220700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>253300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>354100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>382100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>611600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>877000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1119000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>979900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1300200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1409300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3318800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1218400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>619200</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
@@ -878,89 +882,92 @@
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E9" s="3">
         <v>36600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>32000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>33600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>50500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>75100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>84700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>114600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>122400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>129200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>132100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>127100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>108200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>229700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>71300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>72600</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,89 +977,92 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E10" s="3">
         <v>258700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>289200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>301300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>252700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>258300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>155200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>332100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>218000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>158800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>167300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>234600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>241200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>198500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>202800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>279000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>297400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>497000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>754600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>989800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>847800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1173100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1301100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3089100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1147100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>546600</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1062,8 +1072,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1096,44 +1109,45 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>20900</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>27900</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>27700</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,8 +1202,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,62 +1297,65 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-6600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>-4600</v>
-      </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-22500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-18700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>35900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-6700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>46700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1371,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1372,89 +1392,92 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E15" s="3">
         <v>6300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>10600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>10700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>10000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>10200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>10500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9700</v>
-      </c>
-      <c r="V15" s="3">
-        <v>8700</v>
       </c>
       <c r="W15" s="3">
         <v>8700</v>
       </c>
       <c r="X15" s="3">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="Y15" s="3">
         <v>8500</v>
       </c>
       <c r="Z15" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AA15" s="3">
         <v>27100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>9200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>9400</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1464,8 +1487,11 @@
       <c r="AF15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1495,89 +1521,90 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>314900</v>
+      </c>
+      <c r="E17" s="3">
         <v>349400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>359500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>345000</v>
       </c>
-      <c r="G17" s="3">
-        <v>318300</v>
-      </c>
       <c r="H17" s="3">
+        <v>313600</v>
+      </c>
+      <c r="I17" s="3">
         <v>336300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>295500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>378800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>289300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>269200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>266900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>301700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>329200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>327400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>333000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>440400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>567400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>631800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>725200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>778700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>783000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>910200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>777100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1603100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>525100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>419000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1587,89 +1614,92 @@
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-54200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-38400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-36900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-46100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-106700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-41300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-84000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-74200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-42900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-65000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-106700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-79700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-86300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-185300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-20200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>151800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>340300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>196900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>390000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>632200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1715700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>693300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>200200</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1679,8 +1709,11 @@
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1713,8 +1746,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1757,45 +1791,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-54000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-38500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-33500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-68400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-118600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-138500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-145100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>69300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-68300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-216100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-33100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100300</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,89 +1839,92 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-47800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-32900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-30500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-38400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-97900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-32300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-74500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-64300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-32300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-54300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-96700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-123600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-114600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-207600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-78000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>210500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>60500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>467800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>572400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1526600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>669300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>109300</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1897,8 +1934,11 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1941,45 +1981,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>40400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>36100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>32100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11000</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,89 +2029,92 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-46100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-84100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-77200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-85200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-73900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-58300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-106600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-174100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-160900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-252000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-102900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>179000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>30500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>446100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>548000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1467400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>649500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>89000</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,88 +2124,91 @@
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-16700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-13700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-14200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-8600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-16300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-23500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-28200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>24700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
@@ -2173,8 +2219,11 @@
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2265,89 +2314,92 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-40700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-67500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-65900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-71500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-59800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-49800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-91700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-157800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-137500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-223800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-91300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>14700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>154300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>427900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>547200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1465900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>648600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>89000</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2357,88 +2409,91 @@
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-37500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-32200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-77300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-60100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-34700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>51500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>44900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>547200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1465900</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
         <v>0</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
+      <c r="AC27" s="3">
+        <v>0</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
@@ -2449,8 +2504,11 @@
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2541,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2633,8 +2694,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2725,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2817,8 +2884,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2861,45 +2931,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>54000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>38500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>33500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>68400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>118600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>138500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>145100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-69300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>68300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>216100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>33100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100300</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2909,88 +2979,91 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-32200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-77300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-60100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-34700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>51500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>44900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>547200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1465900</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
         <v>0</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
+      <c r="AC33" s="3">
+        <v>0</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
@@ -3001,8 +3074,11 @@
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3093,88 +3169,91 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-32200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-77300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-60100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-34700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>51500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>44900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>547200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1465900</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
         <v>0</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
+      <c r="AC35" s="3">
+        <v>0</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
@@ -3185,94 +3264,97 @@
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3282,8 +3364,11 @@
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3316,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3350,83 +3436,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>229100</v>
+      </c>
+      <c r="E41" s="3">
         <v>277400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>337200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>459200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>408600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>371500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>421600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>483000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>533200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>603700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>660700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>717200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>719100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>798100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>864000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1143900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>954900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>554100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>419600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>506600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>419300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>630500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>284200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>637500</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,53 +3529,56 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E42" s="3">
         <v>153800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>128000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>140600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>155900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>137100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>131900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>161000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>149300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>155600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>186500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>176000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>173800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>180200</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3534,83 +3624,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1508000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1452800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1219800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1028300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>993900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1137400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1164700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>982400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>860500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>748500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>788200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>693700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>716000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>771800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>145300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>108300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>91800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>116000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>56200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>68100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>65200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>84000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>138100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>118400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3626,8 +3719,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3670,8 +3766,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3718,83 +3814,86 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>36400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>28900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>27500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>124800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>129700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>139900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>156000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>115500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>140100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>116300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>140300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>108700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>94800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>84800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>77200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>57600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3810,53 +3909,56 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4592100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5230500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4950700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4301000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4250900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4485600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4456400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4512300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4019000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3882100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3880900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3897100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4056400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4019500</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3902,16 +4004,19 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E47" s="3">
         <v>18100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>18300</v>
       </c>
       <c r="F47" s="3">
         <v>18300</v>
@@ -3920,65 +4025,65 @@
         <v>18300</v>
       </c>
       <c r="H47" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I47" s="3">
         <v>18200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>18100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>17900</v>
       </c>
       <c r="K47" s="3">
         <v>17900</v>
       </c>
       <c r="L47" s="3">
+        <v>17900</v>
+      </c>
+      <c r="M47" s="3">
         <v>17800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18800</v>
-      </c>
-      <c r="O47" s="3">
-        <v>18300</v>
       </c>
       <c r="P47" s="3">
         <v>18300</v>
       </c>
       <c r="Q47" s="3">
+        <v>18300</v>
+      </c>
+      <c r="R47" s="3">
         <v>3122800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3364900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5286500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7059800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8591600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9581200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9968200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9648100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8219100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6089200</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,83 +4099,86 @@
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E48" s="3">
         <v>88100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>65400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>82700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>85800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>82900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>86000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>89200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>93600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>58000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>109300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>116700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>124200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>128600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>138400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>159900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>161000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>159900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>161600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>158800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>154200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>151400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>132700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,53 +4194,56 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1779800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1691200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1678600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1637900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1636000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1621500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1660700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1542700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1583100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1985900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2042000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2053400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2012000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2028800</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -4140,29 +4251,29 @@
         <v>0</v>
       </c>
       <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
         <v>42200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>42300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>42400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>42600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>42700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>42800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>43000</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4289,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4270,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4362,83 +4479,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E52" s="3">
         <v>218500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>145000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>205000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>217800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>208500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>152000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>258800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>233600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>213800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>147800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
         <v>116500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>160900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>194600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>153700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>201000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>97800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>217400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>121400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>204500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>70400</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4454,8 +4574,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4546,83 +4669,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6696600</v>
+      </c>
+      <c r="E54" s="3">
         <v>7246500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6857900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6245000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6208700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6416700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6344000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6417600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5942800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6193300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6151000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6078500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6203500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6190800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6609900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7378500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9195200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10640200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11812300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12749300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13097600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13298300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10893200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8651300</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4638,8 +4764,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4672,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4706,83 +4836,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>301300</v>
+      </c>
+      <c r="E57" s="3">
         <v>336000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>112800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>337200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>322000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>333100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>349700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>337900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>322300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>108600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>404100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>340600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>371800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>488700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>716000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>643100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>804400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>624400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>715600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>607800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>890800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>442900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>376000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4798,59 +4929,62 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4093600</v>
+        <v>3067700</v>
       </c>
       <c r="E58" s="3">
+        <v>4101300</v>
+      </c>
+      <c r="F58" s="3">
         <v>3702700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3025700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2727300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3241700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1020500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2888600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2986600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2848800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1296300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2186500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2223400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2061100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2146600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2529400</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
@@ -4890,83 +5024,86 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>109200</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>80900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>61100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>61700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>66100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>66500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>67700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>71900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>73000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>78100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>80800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>86000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>72600</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,53 +5119,56 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4429600</v>
+        <v>3369000</v>
       </c>
       <c r="E60" s="3">
+        <v>4437300</v>
+      </c>
+      <c r="F60" s="3">
         <v>4002000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3362900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3049300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3574700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1291600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3238300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3324500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3171100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1535800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2590600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2564000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2432800</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5074,83 +5214,86 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2441200</v>
+        <v>2949200</v>
       </c>
       <c r="E61" s="3">
+        <v>2433500</v>
+      </c>
+      <c r="F61" s="3">
         <v>2419800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2412300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2683900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2337500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4437500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2555400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2001900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2339700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3770300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2660600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2775400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2838900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2289300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2283700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6692500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7754500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9085400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9620900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9971700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9614500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7293300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5325800</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5166,53 +5309,56 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E62" s="3">
         <v>38400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>45700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>83000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>60400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>58400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>66800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>77900</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -5258,8 +5404,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5350,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5442,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5534,83 +5689,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6363500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6909200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6471900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5811700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5769700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5947400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5837400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5825600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5363800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5555900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5446600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5309600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5406200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5349600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6176400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6878900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8650600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10073800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11288800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12214200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12579500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12694100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10893200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7017800</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5626,8 +5784,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5660,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5752,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5844,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5936,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6028,83 +6199,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-656200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-651700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-614400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-592400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-587500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-573600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-550600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-517400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-518200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-486100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-451700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-424500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-408200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-384800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-342100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-265600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-205200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-77200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-29000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-17800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-44800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>42400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3">
         <v>1503700</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6120,8 +6294,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6212,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6304,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6396,83 +6579,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E76" s="3">
         <v>204300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>234500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>259400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>272200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>261600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>272900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>311400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>295300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>321600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>353200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>379200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>389400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>403900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>433500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>499600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>544600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>566400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>523600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>535100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>518100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>604200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3">
         <v>1633500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6488,8 +6674,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6580,94 +6769,97 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6677,88 +6869,91 @@
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-32200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-77300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-60100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-34700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>51500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>44900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>547200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1465900</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
         <v>0</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
+      <c r="AC81" s="3">
+        <v>0</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
@@ -6769,8 +6964,11 @@
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6803,89 +7001,90 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E83" s="3">
         <v>10500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-16300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>11700</v>
       </c>
       <c r="H83" s="3">
         <v>11700</v>
       </c>
       <c r="I83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="J83" s="3">
         <v>-13700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-6600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9700</v>
-      </c>
-      <c r="V83" s="3">
-        <v>8700</v>
       </c>
       <c r="W83" s="3">
         <v>8700</v>
       </c>
       <c r="X83" s="3">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="Y83" s="3">
         <v>8500</v>
       </c>
       <c r="Z83" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AA83" s="3">
         <v>27100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9400</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6895,8 +7094,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6987,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7079,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7171,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7263,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7355,89 +7569,92 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>519700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-169300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-638700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>43400</v>
       </c>
-      <c r="G89" s="3">
-        <v>67600</v>
-      </c>
       <c r="H89" s="3">
+        <v>70600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-176800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>47700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-349200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-278300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-278500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-205400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>163300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-337400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>205400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>45800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1744000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1522500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1148400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>593200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>211400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-392500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1877800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1612600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-418100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>543800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>166200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7447,8 +7664,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7481,89 +7701,90 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-14500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-14300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-16200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7573,8 +7794,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7665,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7757,89 +7984,92 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11400</v>
       </c>
-      <c r="G94" s="3">
-        <v>8700</v>
-      </c>
       <c r="H94" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>28100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>436100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>52000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>6700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>70900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>81200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>6900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>9900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>295000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>71900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>291000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>8000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>143100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>159000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-14400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>2000</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7849,8 +8079,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7883,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7897,74 +8131,74 @@
       <c r="F96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G96" s="3">
-        <v>1100</v>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3">
         <v>400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-86900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-30200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-43600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-19400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-233700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-166600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-490700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-152300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AB96" s="3">
         <v>-1900</v>
       </c>
       <c r="AC96" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="AD96" s="3">
         <v>0</v>
@@ -7975,8 +8209,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8067,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8159,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8251,89 +8494,92 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-573700</v>
+      </c>
+      <c r="E100" s="3">
         <v>130300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>522200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>95600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-127200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>324900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-204600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>158700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>112600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-182600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>148400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-304600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-380100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1883700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1152600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1352200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-585000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-386900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>118300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2154300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1407700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1021800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-571500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>360500</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8343,8 +8589,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8387,8 +8636,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8435,89 +8684,92 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-43800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-124900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>47800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-81500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-51400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-52600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-46800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-86100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>51600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-107800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-92300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-324400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>155300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>441700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>87200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>16200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-32300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-115100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>263200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-219200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>590400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>528700</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8525,6 +8777,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
